--- a/data/trans_bre/IP21-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 2,54</t>
+          <t>-4,05; 2,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 2,11</t>
+          <t>-5,11; 2,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 1,79</t>
+          <t>-5,95; 1,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,94</t>
+          <t>-3,34; 1,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-75,59; 181,33</t>
+          <t>-74,72; 208,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-81,22; 106,12</t>
+          <t>-81,17; 101,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-82,13; 78,66</t>
+          <t>-83,07; 88,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-86,41; 242,86</t>
+          <t>-86,98; 259,67</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 4,31</t>
+          <t>-2,23; 4,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 5,52</t>
+          <t>-0,87; 5,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 4,56</t>
+          <t>-0,68; 4,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,98</t>
+          <t>-3,35; 0,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,34; 137,66</t>
+          <t>-39,3; 156,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 300,53</t>
+          <t>-26,67; 284,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 326,58</t>
+          <t>-24,25; 334,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 240,17</t>
+          <t>-100,0; 179,78</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 3,71</t>
+          <t>-4,02; 3,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 1,44</t>
+          <t>-5,81; 1,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,48</t>
+          <t>-2,38; 2,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,93</t>
+          <t>0,81; 5,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-61,29; 133,15</t>
+          <t>-60,45; 136,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-77,91; 43,58</t>
+          <t>-74,09; 54,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,41; 599,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,51; -0,47</t>
+          <t>-6,37; -0,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 2,5</t>
+          <t>-4,41; 2,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,69</t>
+          <t>-2,41; 2,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,54; -0,36</t>
+          <t>-4,38; -0,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-90,51; -2,79</t>
+          <t>-89,96; -10,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,63; 90,0</t>
+          <t>-67,05; 76,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-67,06; 263,54</t>
+          <t>-69,25; 221,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 113,32</t>
+          <t>-100,0; 107,49</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,96</t>
+          <t>-2,5; 0,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,27</t>
+          <t>-2,0; 1,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,72</t>
+          <t>-1,26; 1,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,8</t>
+          <t>-1,39; 0,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-44,93; 26,77</t>
+          <t>-46,74; 22,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,92; 34,49</t>
+          <t>-39,27; 35,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 81,72</t>
+          <t>-36,15; 77,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-60,53; 80,43</t>
+          <t>-61,65; 76,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 2,42</t>
+          <t>-3,98; 2,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 2,09</t>
+          <t>-5,48; 1,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 1,92</t>
+          <t>-5,58; 1,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,71</t>
+          <t>-3,0; 2,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-74,72; 208,95</t>
+          <t>-78,78; 165,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-81,17; 101,78</t>
+          <t>-80,45; 106,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-83,07; 88,41</t>
+          <t>-80,78; 93,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-86,98; 259,67</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 4,82</t>
+          <t>-2,41; 4,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 5,09</t>
+          <t>-0,83; 5,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 4,65</t>
+          <t>-0,98; 4,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,97</t>
+          <t>-3,16; 1,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,3; 156,54</t>
+          <t>-39,87; 148,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,67; 284,71</t>
+          <t>-23,84; 309,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 334,46</t>
+          <t>-29,7; 291,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 179,78</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 3,82</t>
+          <t>-3,97; 3,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 1,66</t>
+          <t>-5,65; 1,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,69</t>
+          <t>-2,5; 2,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,42</t>
+          <t>0,85; 5,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-60,45; 136,84</t>
+          <t>-58,75; 143,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-74,09; 54,42</t>
+          <t>-73,78; 54,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-80,41; 599,63</t>
+          <t>-84,64; 479,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -0,63</t>
+          <t>-6,38; -0,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 2,32</t>
+          <t>-4,18; 2,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,51</t>
+          <t>-2,48; 2,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,38; -0,29</t>
+          <t>-4,59; -0,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-89,96; -10,34</t>
+          <t>-89,64; 0,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,05; 76,15</t>
+          <t>-65,59; 81,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 221,92</t>
+          <t>-69,3; 242,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 107,49</t>
+          <t>-100,0; 188,16</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 0,82</t>
+          <t>-2,65; 0,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,27</t>
+          <t>-2,2; 1,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,67</t>
+          <t>-1,07; 1,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,81</t>
+          <t>-1,36; 0,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,74; 22,96</t>
+          <t>-48,52; 24,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 35,48</t>
+          <t>-40,67; 34,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,15; 77,76</t>
+          <t>-31,76; 88,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-61,65; 76,95</t>
+          <t>-58,23; 94,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-23,59%</t>
+          <t>-25,65%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 2,81</t>
+          <t>-4,09; 2,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 1,96</t>
+          <t>-5,32; 2,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 1,87</t>
+          <t>-5,45; 1,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,3</t>
+          <t>-3,13; 1,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-78,78; 165,05</t>
+          <t>-75,59; 181,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,45; 106,02</t>
+          <t>-81,22; 106,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-80,78; 93,47</t>
+          <t>-82,13; 78,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,11; 225,68</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-45,42%</t>
+          <t>-48,94%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 4,48</t>
+          <t>-2,32; 4,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 5,34</t>
+          <t>-0,68; 5,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,59</t>
+          <t>-0,77; 4,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,09</t>
+          <t>-3,36; 0,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,87; 148,48</t>
+          <t>-40,34; 137,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 309,1</t>
+          <t>-22,86; 300,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,7; 291,97</t>
+          <t>-26,7; 326,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 219,54</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>2,83</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 3,88</t>
+          <t>-4,01; 3,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 1,73</t>
+          <t>-6,32; 1,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 2,53</t>
+          <t>-2,19; 2,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,26</t>
+          <t>1,17; 5,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-58,75; 143,81</t>
+          <t>-61,29; 133,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-73,78; 54,23</t>
+          <t>-77,91; 43,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-84,64; 479,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,08</t>
+          <t>-2,01</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-82,52%</t>
+          <t>-82,71%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,38; -0,44</t>
+          <t>-6,51; -0,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 2,36</t>
+          <t>-4,44; 2,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,65</t>
+          <t>-2,31; 2,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,59; -0,29</t>
+          <t>-4,41; -0,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-89,64; 0,64</t>
+          <t>-90,51; -2,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,59; 81,15</t>
+          <t>-64,63; 90,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-69,3; 242,74</t>
+          <t>-67,06; 263,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 188,16</t>
+          <t>-100,0; 48,1</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-15,26%</t>
+          <t>-13,0%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,9</t>
+          <t>-2,4; 0,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,21</t>
+          <t>-2,1; 1,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,73</t>
+          <t>-1,09; 1,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,93</t>
+          <t>-1,28; 0,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-48,52; 24,44</t>
+          <t>-44,93; 26,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 34,56</t>
+          <t>-40,92; 34,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,76; 88,49</t>
+          <t>-31,15; 81,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-58,23; 94,66</t>
+          <t>-59,93; 85,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,66</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,52</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-19,16%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-34,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-35,18%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-25,65%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.659269385892617</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.524680658031843</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.603927231883735</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.5467309929518792</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.1915521507586224</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.3405530912214124</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.3517611976741512</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.2564860194588551</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-4,09; 2,54</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,32; 2,11</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,45; 1,79</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-3,13; 1,82</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-75,59; 181,33</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-81,22; 106,12</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-82,13; 78,66</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-90,11; 225,68</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.088679226355419</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.324456905795381</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.447170045918479</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.127926183519076</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.7559252826097769</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.8122316545098982</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.8212681330752263</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.9011391236109575</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.540092003876776</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.108143387271193</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.792027105378569</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.821790804687317</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.813279133778483</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.061156334328885</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.786550151776809</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>2.256823726197912</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,1</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,12</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>23,97%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>71,33%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>64,64%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-48,94%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,32; 4,31</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-0,68; 5,52</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,77; 4,56</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,36; 0,87</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-40,34; 137,66</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-22,86; 300,53</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-26,7; 326,58</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 219,54</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.100281827739051</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.118476493059844</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.72603388255623</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.9338971156656328</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.2396719679142607</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.7132675861940305</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.6463948840385254</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.4894454585447763</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,15</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,83</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,26%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-36,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.31603745167956</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.6805893482612422</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.7685085224849857</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.363600983355124</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4034376294038226</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2286217230355486</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.2670085730896137</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,01; 3,71</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,32; 1,44</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,19; 2,48</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,17; 5,78</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-61,29; 133,15</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-77,91; 43,58</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.310263798272658</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.519631290380712</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.560291502344003</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.8650107927850181</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.376642064109308</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>3.005268445973012</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>3.265787807855484</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>2.195402708300174</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,44 +819,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-3,4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,87</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,01</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-65,54%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-18,18%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-82,71%</t>
+      <c r="C10" s="5" t="n">
+        <v>-0.0620158459475377</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.147711449255158</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1593287004377782</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.8346590588901</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.01258509196731177</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.3625189319416751</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.08956751654684729</v>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -955,152 +850,260 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-6,51; -0,47</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,44; 2,5</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,31; 2,69</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,41; -0,37</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-90,51; -2,79</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-64,63; 90,0</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-67,06; 263,54</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 48,1</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.008425869842461</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.322370779629703</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.194543988741789</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1.168413246963961</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.6129284307555125</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.7790862646456025</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.713371297460281</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.441521769050961</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.478535214710762</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.784677255536285</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.3314797700667</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.4357772054653638</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-3.396931889673897</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.8685054134346871</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.07316955416757989</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.009250159144333</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.655404207082811</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1817836538489936</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.03017010113191498</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.8270959489833548</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-6.514753330445616</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.435341220799676</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.30873133635937</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.409661221907648</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.9051125715633052</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6463115670531775</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6706176988544662</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-0.4734140843981134</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.500570720707637</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.686450514096473</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-0.3715514483495395</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.02788132046949092</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.8999748969428097</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.635429526411198</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.4810046943243345</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,86</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-18,66%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-8,92%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-13,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,4; 0,96</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,1; 1,27</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,09; 1,72</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,28; 0,87</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-44,93; 26,77</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-40,92; 34,49</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-31,15; 81,72</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-59,93; 85,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.8561467197220396</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.3951512116622042</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.2402932192317277</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.2100742091025754</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1866276102706194</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.08919723896881013</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.08647577327940296</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1300063969634311</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.398571950441772</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.101441857150952</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.087424158193255</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.2787855173234</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4492504916061691</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4091779343206032</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.3115208350124237</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.5993129646885894</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9585977557150264</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.271333278005857</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.716591906254494</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.8725977201778876</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.2676552916366228</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.3448907100413863</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.8171663722079819</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.8508486477832351</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1111,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
